--- a/slt_yield_output.xlsx
+++ b/slt_yield_output.xlsx
@@ -10,6 +10,7 @@
     <sheet name="工序汇总" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="月度良率" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="温度分类汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="温度Qty合并" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5171,4 +5172,1513 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>YearMonth</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>温度类型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PassQty</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TestQty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FailQty</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Yield</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FDPPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3139</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3224</v>
+      </c>
+      <c r="E2" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9736352357320099</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>26364.76426799007</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4035</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4113</v>
+      </c>
+      <c r="E3" t="n">
+        <v>78</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9810357403355215</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>18964.25966447848</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4359</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4534</v>
+      </c>
+      <c r="E4" t="n">
+        <v>175</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9614027348919276</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>38597.26510807234</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1771</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1870</v>
+      </c>
+      <c r="E5" t="n">
+        <v>99</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9470588235294117</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>52941.17647058824</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6132</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6343</v>
+      </c>
+      <c r="E6" t="n">
+        <v>211</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9667349834463188</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>33265.01655368122</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6371</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6665</v>
+      </c>
+      <c r="E7" t="n">
+        <v>294</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.9558889722430608</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>44111.02775693923</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5803</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6180</v>
+      </c>
+      <c r="E8" t="n">
+        <v>377</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.9389967637540453</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>61003.23624595469</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4599</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4712</v>
+      </c>
+      <c r="E9" t="n">
+        <v>113</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.976018675721562</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>23981.32427843803</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5545</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5734</v>
+      </c>
+      <c r="E10" t="n">
+        <v>189</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.9670387164283223</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>32961.28357167771</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5216</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5269</v>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.9899411653065098</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>10058.83469349023</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5485</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5867</v>
+      </c>
+      <c r="E12" t="n">
+        <v>382</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9348900630645987</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>65109.93693540141</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4934</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5215</v>
+      </c>
+      <c r="E13" t="n">
+        <v>281</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.9461169702780441</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>53883.0297219559</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5207</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5337</v>
+      </c>
+      <c r="E14" t="n">
+        <v>130</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9756417462994191</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>24358.25370058085</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7092</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7501</v>
+      </c>
+      <c r="E15" t="n">
+        <v>409</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.9454739368084255</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>54526.06319157446</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5037</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5172</v>
+      </c>
+      <c r="E16" t="n">
+        <v>135</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.9738979118329466</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>26102.08816705336</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4555</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E17" t="n">
+        <v>245</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.9489583333333333</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>51041.66666666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3988</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4063</v>
+      </c>
+      <c r="E18" t="n">
+        <v>75</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.981540733448191</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>18459.26655180901</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4803</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4970</v>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.9663983903420523</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>33601.60965794769</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8704</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8975</v>
+      </c>
+      <c r="E20" t="n">
+        <v>271</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.9698050139275766</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>30194.9860724234</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6830</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7086</v>
+      </c>
+      <c r="E21" t="n">
+        <v>256</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0.9638724244990121</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>36127.57550098786</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5205</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5320</v>
+      </c>
+      <c r="E22" t="n">
+        <v>115</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.9783834586466166</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>21616.54135338346</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4622</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4885</v>
+      </c>
+      <c r="E23" t="n">
+        <v>263</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0.9461617195496418</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>53838.28045035824</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5447</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5853</v>
+      </c>
+      <c r="E24" t="n">
+        <v>406</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.9306338629762515</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>69366.13702374851</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5612</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5769</v>
+      </c>
+      <c r="E25" t="n">
+        <v>157</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0.9727855780897903</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>27214.42191020974</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6402</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6744</v>
+      </c>
+      <c r="E26" t="n">
+        <v>342</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0.949288256227758</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>50711.74377224199</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4891</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5152</v>
+      </c>
+      <c r="E27" t="n">
+        <v>261</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.9493400621118012</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>50659.93788819876</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5461</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5690</v>
+      </c>
+      <c r="E28" t="n">
+        <v>229</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.9597539543057997</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>40246.04569420035</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3562</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3811</v>
+      </c>
+      <c r="E29" t="n">
+        <v>249</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0.9346628181579638</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>65337.18184203621</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6266</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6543</v>
+      </c>
+      <c r="E30" t="n">
+        <v>277</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0.9576646798104845</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>42335.32018951551</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6454</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6624</v>
+      </c>
+      <c r="E31" t="n">
+        <v>170</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.9743357487922706</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>25664.25120772947</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3539</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3723</v>
+      </c>
+      <c r="E32" t="n">
+        <v>184</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9505774912704807</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>49422.50872951921</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5051</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5367</v>
+      </c>
+      <c r="E33" t="n">
+        <v>316</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0.9411216694615241</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>58878.33053847586</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5471</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5762</v>
+      </c>
+      <c r="E34" t="n">
+        <v>291</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.9494967025338424</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>50503.29746615759</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7348</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7575</v>
+      </c>
+      <c r="E35" t="n">
+        <v>227</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0.97003300330033</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>29966.99669966997</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4935</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5218</v>
+      </c>
+      <c r="E36" t="n">
+        <v>283</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.9457646607895746</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>54235.33921042545</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7708</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8100</v>
+      </c>
+      <c r="E37" t="n">
+        <v>392</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0.951604938271605</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>48395.06172839506</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5741</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6096</v>
+      </c>
+      <c r="E38" t="n">
+        <v>355</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.9417650918635171</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>58234.90813648294</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>6641</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7140</v>
+      </c>
+      <c r="E39" t="n">
+        <v>499</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0.9301120448179272</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>69887.95518207284</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5844</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6220</v>
+      </c>
+      <c r="E40" t="n">
+        <v>376</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0.9395498392282958</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>60450.16077170418</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4638</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4831</v>
+      </c>
+      <c r="E41" t="n">
+        <v>193</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0.9600496791554544</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>39950.32084454565</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>6989</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7183</v>
+      </c>
+      <c r="E42" t="n">
+        <v>194</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.9729917861617708</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>27008.21383822915</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3465</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3498</v>
+      </c>
+      <c r="E43" t="n">
+        <v>33</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0.9905660377358491</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>9433.962264150943</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4166</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4363</v>
+      </c>
+      <c r="E44" t="n">
+        <v>197</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.9548475819390327</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>45152.41806096723</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3423</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3612</v>
+      </c>
+      <c r="E45" t="n">
+        <v>189</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0.9476744186046512</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>52325.58139534884</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5884</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6052</v>
+      </c>
+      <c r="E46" t="n">
+        <v>168</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.9722405816259088</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>27759.41837409121</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>8369</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8841</v>
+      </c>
+      <c r="E47" t="n">
+        <v>472</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0.9466123741658183</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>53387.62583418166</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3506</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3602</v>
+      </c>
+      <c r="E48" t="n">
+        <v>96</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.9733481399222654</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>26651.86007773459</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>5786</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5937</v>
+      </c>
+      <c r="E49" t="n">
+        <v>151</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0.9745662792656223</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>25433.72073437763</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5224</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5527</v>
+      </c>
+      <c r="E50" t="n">
+        <v>303</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0.9451782160303962</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>54821.78396960376</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4614</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4776</v>
+      </c>
+      <c r="E51" t="n">
+        <v>162</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0.9660804020100503</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>33919.59798994975</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3615</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3775</v>
+      </c>
+      <c r="E52" t="n">
+        <v>160</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.9576158940397351</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>42384.1059602649</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6170</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6380</v>
+      </c>
+      <c r="E53" t="n">
+        <v>210</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0.9670846394984326</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>32915.3605015674</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>低温</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4638</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5005</v>
+      </c>
+      <c r="E54" t="n">
+        <v>367</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0.9266733266733267</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>73326.67332667332</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>高温</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>4766</v>
+      </c>
+      <c r="D55" t="n">
+        <v>4884</v>
+      </c>
+      <c r="E55" t="n">
+        <v>118</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0.9758394758394758</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>24160.52416052416</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/slt_yield_output.xlsx
+++ b/slt_yield_output.xlsx
@@ -4012,7 +4012,7 @@
         <v>0.9776148205326128</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.8423774612432049</v>
+        <v>0.9183039773703625</v>
       </c>
     </row>
     <row r="3">
@@ -4040,7 +4040,7 @@
         <v>0.9743518260384723</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.752440651580465</v>
+        <v>0.8751688286530833</v>
       </c>
     </row>
     <row r="4">
@@ -4068,7 +4068,7 @@
         <v>0.9220636663007684</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.7426497877689586</v>
+        <v>0.8862700741659014</v>
       </c>
     </row>
     <row r="5">
@@ -4096,7 +4096,7 @@
         <v>0.9311768754301445</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.7605397025011097</v>
+        <v>0.8756181602798898</v>
       </c>
     </row>
     <row r="6">
@@ -4124,7 +4124,7 @@
         <v>0.9494219653179191</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7890697530272105</v>
+        <v>0.8983661322747416</v>
       </c>
     </row>
     <row r="7">
@@ -4152,7 +4152,7 @@
         <v>0.9350282485875706</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7902789289000985</v>
+        <v>0.9001433329239529</v>
       </c>
     </row>
     <row r="8">
@@ -4180,7 +4180,7 @@
         <v>0.9768399382398353</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8215735297033068</v>
+        <v>0.9145618522353045</v>
       </c>
     </row>
     <row r="9">
@@ -4208,7 +4208,7 @@
         <v>0.9840989399293286</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.7455009973510003</v>
+        <v>0.8565670174372157</v>
       </c>
     </row>
     <row r="10">
@@ -4236,7 +4236,7 @@
         <v>0.9441887226697353</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.732277766510414</v>
+        <v>0.8649277415110558</v>
       </c>
     </row>
     <row r="11">
@@ -4264,7 +4264,7 @@
         <v>0.9571365444100751</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.7419074511228507</v>
+        <v>0.8721216622860662</v>
       </c>
     </row>
     <row r="12">
@@ -4292,7 +4292,7 @@
         <v>0.9502487562189055</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.7223329077947148</v>
+        <v>0.8494283672792518</v>
       </c>
     </row>
     <row r="13">
@@ -4320,7 +4320,7 @@
         <v>0.9339050407864463</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.7742544566518542</v>
+        <v>0.8730241947835174</v>
       </c>
     </row>
     <row r="14">
@@ -4348,7 +4348,7 @@
         <v>0.9205998033431662</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.7108180212382764</v>
+        <v>0.8229959150090398</v>
       </c>
     </row>
     <row r="15">
@@ -4376,7 +4376,7 @@
         <v>0.9906759906759907</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.8427054810433524</v>
+        <v>0.925307995029977</v>
       </c>
     </row>
     <row r="16">
@@ -4404,7 +4404,7 @@
         <v>0.9768835616438356</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.7676934532693601</v>
+        <v>0.8797655561270066</v>
       </c>
     </row>
     <row r="17">
@@ -4432,7 +4432,7 @@
         <v>0.9906600249066002</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.8042451735792283</v>
+        <v>0.8979491856990314</v>
       </c>
     </row>
     <row r="18">
@@ -4460,7 +4460,7 @@
         <v>0.9618913196894848</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.7762497753005356</v>
+        <v>0.8744164544512163</v>
       </c>
     </row>
     <row r="19">
@@ -4488,7 +4488,7 @@
         <v>0.9669459962756052</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.7732612759925773</v>
+        <v>0.8745195659131253</v>
       </c>
     </row>
   </sheetData>
